--- a/artfynd/A 51105-2025 artfynd.xlsx
+++ b/artfynd/A 51105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129892505</v>
       </c>
       <c r="B2" t="n">
-        <v>57749</v>
+        <v>57750</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51105-2025 artfynd.xlsx
+++ b/artfynd/A 51105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129892505</v>
       </c>
       <c r="B2" t="n">
-        <v>57750</v>
+        <v>57753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51105-2025 artfynd.xlsx
+++ b/artfynd/A 51105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129892505</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57839</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51105-2025 artfynd.xlsx
+++ b/artfynd/A 51105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129892505</v>
       </c>
       <c r="B2" t="n">
-        <v>57839</v>
+        <v>57754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 51105-2025 artfynd.xlsx
+++ b/artfynd/A 51105-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129892505</v>
       </c>
       <c r="B2" t="n">
-        <v>57754</v>
+        <v>57966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
